--- a/src/app/modules/dashboard/excel_files/quick-10-minute-fat-burning-whole-food-plant-based-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/quick-10-minute-fat-burning-whole-food-plant-based-recipes.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -16972,7 +16972,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -17245,7 +17245,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'smoothies/shakes', 'wraps', 'bowls', 'salads', 'sandwiches', 'desserts']</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
